--- a/docs/03_Bug记录表.xlsx
+++ b/docs/03_Bug记录表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MoodBoard-Complete\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A8B69A-E74E-4E26-B0B1-86F7565D387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D65DFE-38DB-4334-B84C-867C8A6B72FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5423" yWindow="390" windowWidth="16200" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bug记录" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="164">
   <si>
     <t>MoodBoard × MBTI 项目 Bug 记录表</t>
   </si>
@@ -433,6 +433,186 @@
   </si>
   <si>
     <t>DiaryPage 不同视图分别请求数据，数据源未统一，导致周/月/年视图展示不一致</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>登录注册模块</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>注册成功后自动登录失败，提示未获取到 token</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>前端、后端服务正常启动，用户未登录</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 进入登录页；2. 切换到注册；3. 输入新用户名和密码；4. 点击注册</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面提示“注册成功，但自动登录失败，请手动登录”，用户未自动进入系统</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>注册成功后应自动登录，并跳转到系统首页或情绪日记页</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>游客登录模块</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击游客登录后提示未获取到 token，无法进入系统</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>V2.0</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 进入登录页；2. 点击“游客登录”按钮</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击游客登录后，应自动创建游客账号并进入系统</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>页面提示“游客登录失败：未获取到 token”，无法进入系统</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI聊天 / 会话记录模块</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同账号登录后可看到同一浏览器下其他账号的聊天记录</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>浏览器 localStorage 中存在历史聊天记录</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 登录账号A；2. 在日常树洞或人格聊天中发送消息；3. 切换登录账号B；4. 进入同一聊天页面</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>不同账号之间的聊天记录应隔离显示，账号B不应看到账号A的数据</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号B可以看到账号A的聊天记录</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG-007</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG-008</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG-009</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG-010</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAG 情绪知识库</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击 RAG 生成回答时接口返回 500</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入情绪知识库页面，输入“我最近考试很焦虑怎么办”，点击 RAG 生成回答</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统应返回基于知识库的 AI 回答</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>前端弹出“RAG 回答生成失败，请检查后端接口或 DeepSeek 配置</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG-011</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI聊天</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>用户输入内容未正确传给后端，AI 返回“请输入你想说的话”</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>在日常树洞输入“最近睡不着”并发送</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 应根据用户输入生成情绪疏导回复</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 回复“请输入你想说的话”</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG-012</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>人格对战 / Agent圆桌</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>人格选择区和聊天区混在同一页面，导致页面显示不完整</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入人格对话，点击人格对战</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择人格和正式聊天应分步展示，页面结构清晰</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择人格卡片、聊天区、输入框挤在同一页，底部内容显示不完整</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUG-013</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>GitHub / 项目配置</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>README 中包含 DeepSeek API Key，导致 GitHub Secret Scanning 拦截 push</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行 git push 上传项目</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>GitHub 拒绝推送，提示检测到 DeepSeek API Key</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目应正常上传 GitHub，且不包含敏感密钥</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1577,143 +1757,313 @@
       <c r="S10" s="3"/>
     </row>
     <row r="11" spans="1:19" ht="72" customHeight="1">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="A11" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
+      <c r="N11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="3"/>
     </row>
     <row r="12" spans="1:19" ht="72" customHeight="1">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="A12" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+      <c r="N12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="3"/>
     </row>
     <row r="13" spans="1:19" ht="72" customHeight="1">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="A13" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
+      <c r="N13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="3"/>
     </row>
     <row r="14" spans="1:19" ht="72" customHeight="1">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
+      <c r="A14" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="I14" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
+      <c r="N14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
       <c r="S14" s="3"/>
     </row>
     <row r="15" spans="1:19" ht="72" customHeight="1">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
+      <c r="A15" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="I15" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
+      <c r="N15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="3"/>
     </row>
     <row r="16" spans="1:19" ht="72" customHeight="1">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="A16" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="I16" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K16" t="s">
+        <v>157</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
+      <c r="N16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
       <c r="S16" s="3"/>
     </row>
     <row r="17" spans="1:19" ht="72" customHeight="1">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="I17" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>162</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
@@ -2636,7 +2986,7 @@
       </c>
       <c r="B4" s="6">
         <f>COUNTA(Bug记录!$C$5:$C$54)</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>1</v>
@@ -2675,7 +3025,7 @@
       </c>
       <c r="E5" s="6">
         <f>COUNTIFS(Bug记录!$C$5:$C$54,"*",Bug记录!$D$5:$D$54,"中")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>1</v>
@@ -2694,7 +3044,7 @@
       </c>
       <c r="B6" s="6">
         <f>COUNTIFS(Bug记录!$C$5:$C$54,"*",Bug记录!$E$5:$E$54,"P1")</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>1</v>
@@ -2704,7 +3054,7 @@
       </c>
       <c r="E6" s="6">
         <f>COUNTIFS(Bug记录!$C$5:$C$54,"*",Bug记录!$D$5:$D$54,"高")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>1</v>
@@ -2714,7 +3064,7 @@
       </c>
       <c r="H6" s="6">
         <f>COUNTIFS(Bug记录!$C$5:$C$54,"*",Bug记录!$O$5:$O$54,"已修复")</f>
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2723,7 +3073,7 @@
       </c>
       <c r="B7" s="6">
         <f>COUNTIFS(Bug记录!$C$5:$C$54,"*",Bug记录!$E$5:$E$54,"P2")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1</v>
@@ -2799,7 +3149,7 @@
       </c>
       <c r="H9" s="6">
         <f>B4-H7</f>
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
